--- a/docs/secc_trade_fairs.xlsx
+++ b/docs/secc_trade_fairs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECC events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SECC events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SECC events'!$A$1:$K$30</definedName>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Exhibition Hall A Exhibition Hall B</t>
+          <t>Exhibition Hall A, Exhibition Hall B</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Exhibition Hall A Exhibition Hall B</t>
+          <t>Exhibition Hall A, Exhibition Hall B</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Exhibition Hall A Exhibition Hall B1</t>
+          <t>Exhibition Hall A, Exhibition Hall B1</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Exhibition Hall A Exhibition Hall B1</t>
+          <t>Exhibition Hall A, Exhibition Hall B1</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exhibition Hall A Exhibition Hall B</t>
+          <t>Exhibition Hall A, Exhibition Hall B</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exhibition Hall A Exhibition Hall B</t>
+          <t>Exhibition Hall A, Exhibition Hall B</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
